--- a/DataAgent Multi-species/data.xlsx
+++ b/DataAgent Multi-species/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\【农科发现大模型】\Data-Agent\绘图\replot_with_AdobeAI\plot-20260626-multi-species\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E58C9E-3946-4A8D-BD14-F05E522E851E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F7C6FD-820E-4295-B93B-93B54BE18011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-7035" windowWidth="21840" windowHeight="37920" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -497,16 +497,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="b">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="b">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="b">
         <v>1</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="3" t="b">
         <v>1</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="3" t="b">
         <v>1</v>
@@ -2376,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="3" t="b">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3" t="b">
         <v>1</v>
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="C188" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" s="3" t="b">
         <v>0</v>
@@ -7720,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="C216" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D216" s="3" t="b">
         <v>0</v>
@@ -10472,7 +10472,7 @@
         <v>0</v>
       </c>
       <c r="C302" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302" s="3" t="b">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         <v>0</v>
       </c>
       <c r="C416" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D416" s="3" t="b">
         <v>1</v>
@@ -17864,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="C533" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D533" s="3" t="b">
         <v>1</v>
@@ -18408,7 +18408,7 @@
         <v>1</v>
       </c>
       <c r="C550" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D550" s="3" t="b">
         <v>0</v>
@@ -18824,7 +18824,7 @@
         <v>1</v>
       </c>
       <c r="C563" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D563" s="3" t="b">
         <v>0</v>
@@ -18856,7 +18856,7 @@
         <v>1</v>
       </c>
       <c r="C564" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D564" s="3" t="b">
         <v>0</v>
@@ -18888,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="C565" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D565" s="3" t="b">
         <v>0</v>
@@ -18920,7 +18920,7 @@
         <v>1</v>
       </c>
       <c r="C566" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D566" s="3" t="b">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>1</v>
       </c>
       <c r="C569" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D569" s="3" t="b">
         <v>0</v>
@@ -19048,7 +19048,7 @@
         <v>1</v>
       </c>
       <c r="C570" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D570" s="3" t="b">
         <v>0</v>
@@ -19080,7 +19080,7 @@
         <v>0</v>
       </c>
       <c r="C571" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D571" s="3" t="b">
         <v>0</v>
@@ -19112,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="C572" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D572" s="3" t="b">
         <v>0</v>
@@ -19144,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="C573" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D573" s="3" t="b">
         <v>0</v>
@@ -19176,7 +19176,7 @@
         <v>1</v>
       </c>
       <c r="C574" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D574" s="3" t="b">
         <v>0</v>
@@ -19240,7 +19240,7 @@
         <v>0</v>
       </c>
       <c r="C576" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D576" s="3" t="b">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>1</v>
       </c>
       <c r="C577" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D577" s="3" t="b">
         <v>0</v>
@@ -19336,7 +19336,7 @@
         <v>1</v>
       </c>
       <c r="C579" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D579" s="3" t="b">
         <v>1</v>
@@ -19432,7 +19432,7 @@
         <v>1</v>
       </c>
       <c r="C582" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D582" s="3" t="b">
         <v>1</v>
@@ -19464,7 +19464,7 @@
         <v>1</v>
       </c>
       <c r="C583" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D583" s="3" t="b">
         <v>0</v>
@@ -19496,7 +19496,7 @@
         <v>1</v>
       </c>
       <c r="C584" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D584" s="3" t="b">
         <v>1</v>
@@ -19528,7 +19528,7 @@
         <v>1</v>
       </c>
       <c r="C585" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D585" s="3" t="b">
         <v>0</v>
@@ -19624,7 +19624,7 @@
         <v>1</v>
       </c>
       <c r="C588" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D588" s="3" t="b">
         <v>1</v>
@@ -19656,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="C589" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D589" s="3" t="b">
         <v>1</v>
@@ -19720,7 +19720,7 @@
         <v>1</v>
       </c>
       <c r="C591" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D591" s="3" t="b">
         <v>1</v>
@@ -20104,7 +20104,7 @@
         <v>1</v>
       </c>
       <c r="C603" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D603" s="3" t="b">
         <v>0</v>
@@ -20744,7 +20744,7 @@
         <v>1</v>
       </c>
       <c r="C623" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D623" s="3" t="b">
         <v>1</v>
@@ -21096,7 +21096,7 @@
         <v>1</v>
       </c>
       <c r="C634" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D634" s="3" t="b">
         <v>1</v>
@@ -21192,7 +21192,7 @@
         <v>1</v>
       </c>
       <c r="C637" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D637" s="3" t="b">
         <v>1</v>
@@ -21480,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="C646" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D646" s="3" t="b">
         <v>0</v>
@@ -21704,7 +21704,7 @@
         <v>0</v>
       </c>
       <c r="C653" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D653" s="3" t="b">
         <v>1</v>
@@ -21736,7 +21736,7 @@
         <v>1</v>
       </c>
       <c r="C654" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D654" s="3" t="b">
         <v>1</v>
@@ -21896,7 +21896,7 @@
         <v>0</v>
       </c>
       <c r="C659" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D659" s="3" t="b">
         <v>1</v>
@@ -21928,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="C660" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D660" s="3" t="b">
         <v>1</v>
@@ -21960,7 +21960,7 @@
         <v>1</v>
       </c>
       <c r="C661" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D661" s="3" t="b">
         <v>1</v>
@@ -22024,7 +22024,7 @@
         <v>1</v>
       </c>
       <c r="C663" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D663" s="3" t="b">
         <v>1</v>
@@ -22056,7 +22056,7 @@
         <v>1</v>
       </c>
       <c r="C664" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D664" s="3" t="b">
         <v>1</v>
@@ -22088,7 +22088,7 @@
         <v>1</v>
       </c>
       <c r="C665" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D665" s="3" t="b">
         <v>1</v>
@@ -22152,7 +22152,7 @@
         <v>1</v>
       </c>
       <c r="C667" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D667" s="3" t="b">
         <v>1</v>
@@ -22216,7 +22216,7 @@
         <v>1</v>
       </c>
       <c r="C669" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D669" s="3" t="b">
         <v>1</v>
@@ -22280,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="C671" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D671" s="3" t="b">
         <v>1</v>
@@ -22312,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="C672" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D672" s="3" t="b">
         <v>1</v>
@@ -22344,7 +22344,7 @@
         <v>1</v>
       </c>
       <c r="C673" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D673" s="3" t="b">
         <v>1</v>
@@ -22376,7 +22376,7 @@
         <v>1</v>
       </c>
       <c r="C674" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D674" s="3" t="b">
         <v>0</v>
@@ -22504,7 +22504,7 @@
         <v>1</v>
       </c>
       <c r="C678" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D678" s="3" t="b">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         <v>1</v>
       </c>
       <c r="C679" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D679" s="3" t="b">
         <v>0</v>
@@ -22632,7 +22632,7 @@
         <v>1</v>
       </c>
       <c r="C682" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D682" s="3" t="b">
         <v>1</v>
@@ -22856,7 +22856,7 @@
         <v>1</v>
       </c>
       <c r="C689" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D689" s="3" t="b">
         <v>1</v>
@@ -22888,7 +22888,7 @@
         <v>1</v>
       </c>
       <c r="C690" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D690" s="3" t="b">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>1</v>
       </c>
       <c r="C691" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D691" s="3" t="b">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>1</v>
       </c>
       <c r="C692" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D692" s="3" t="b">
         <v>1</v>
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="C699" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D699" s="3" t="b">
         <v>0</v>
@@ -23208,7 +23208,7 @@
         <v>1</v>
       </c>
       <c r="C700" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D700" s="3" t="b">
         <v>1</v>
@@ -23272,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="C702" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D702" s="3" t="b">
         <v>0</v>
@@ -23304,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="C703" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D703" s="3" t="b">
         <v>0</v>
@@ -23368,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="C705" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D705" s="3" t="b">
         <v>1</v>
@@ -23464,7 +23464,7 @@
         <v>1</v>
       </c>
       <c r="C708" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D708" s="3" t="b">
         <v>1</v>
@@ -23496,7 +23496,7 @@
         <v>1</v>
       </c>
       <c r="C709" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D709" s="3" t="b">
         <v>0</v>
@@ -23560,7 +23560,7 @@
         <v>0</v>
       </c>
       <c r="C711" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D711" s="3" t="b">
         <v>0</v>
@@ -23592,7 +23592,7 @@
         <v>1</v>
       </c>
       <c r="C712" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D712" s="3" t="b">
         <v>0</v>
@@ -23688,7 +23688,7 @@
         <v>1</v>
       </c>
       <c r="C715" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D715" s="3" t="b">
         <v>0</v>
@@ -23752,7 +23752,7 @@
         <v>1</v>
       </c>
       <c r="C717" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D717" s="3" t="b">
         <v>1</v>
@@ -23976,7 +23976,7 @@
         <v>1</v>
       </c>
       <c r="C724" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D724" s="3" t="b">
         <v>1</v>
@@ -24040,7 +24040,7 @@
         <v>1</v>
       </c>
       <c r="C726" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D726" s="3" t="b">
         <v>0</v>
@@ -24072,7 +24072,7 @@
         <v>1</v>
       </c>
       <c r="C727" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D727" s="3" t="b">
         <v>0</v>
@@ -24104,7 +24104,7 @@
         <v>1</v>
       </c>
       <c r="C728" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D728" s="3" t="b">
         <v>1</v>
@@ -24136,7 +24136,7 @@
         <v>1</v>
       </c>
       <c r="C729" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D729" s="3" t="b">
         <v>1</v>
@@ -24168,7 +24168,7 @@
         <v>1</v>
       </c>
       <c r="C730" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D730" s="3" t="b">
         <v>1</v>
@@ -24264,7 +24264,7 @@
         <v>1</v>
       </c>
       <c r="C733" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D733" s="3" t="b">
         <v>1</v>
@@ -24296,7 +24296,7 @@
         <v>1</v>
       </c>
       <c r="C734" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D734" s="3" t="b">
         <v>1</v>
@@ -24328,7 +24328,7 @@
         <v>1</v>
       </c>
       <c r="C735" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D735" s="3" t="b">
         <v>1</v>
@@ -24360,7 +24360,7 @@
         <v>1</v>
       </c>
       <c r="C736" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D736" s="3" t="b">
         <v>1</v>
@@ -24488,7 +24488,7 @@
         <v>1</v>
       </c>
       <c r="C740" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D740" s="3" t="b">
         <v>1</v>
@@ -24520,7 +24520,7 @@
         <v>1</v>
       </c>
       <c r="C741" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D741" s="3" t="b">
         <v>1</v>
@@ -25224,7 +25224,7 @@
         <v>1</v>
       </c>
       <c r="C763" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D763" s="3" t="b">
         <v>0</v>
@@ -25544,7 +25544,7 @@
         <v>1</v>
       </c>
       <c r="C773" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D773" s="3" t="b">
         <v>0</v>
@@ -25640,7 +25640,7 @@
         <v>1</v>
       </c>
       <c r="C776" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D776" s="3" t="b">
         <v>0</v>
@@ -27016,7 +27016,7 @@
         <v>1</v>
       </c>
       <c r="C819" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D819" s="3" t="b">
         <v>1</v>
@@ -27432,7 +27432,7 @@
         <v>1</v>
       </c>
       <c r="C832" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D832" s="3" t="b">
         <v>1</v>
@@ -27624,7 +27624,7 @@
         <v>0</v>
       </c>
       <c r="C838" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D838" s="3" t="b">
         <v>1</v>
@@ -28040,7 +28040,7 @@
         <v>1</v>
       </c>
       <c r="C851" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D851" s="3" t="b">
         <v>0</v>
@@ -28104,7 +28104,7 @@
         <v>0</v>
       </c>
       <c r="C853" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D853" s="3" t="b">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>0</v>
       </c>
       <c r="C859" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D859" s="3" t="b">
         <v>0</v>
@@ -28488,7 +28488,7 @@
         <v>0</v>
       </c>
       <c r="C865" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D865" s="3" t="b">
         <v>0</v>
@@ -28616,7 +28616,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D869" s="3" t="b">
         <v>0</v>
@@ -28712,7 +28712,7 @@
         <v>0</v>
       </c>
       <c r="C872" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D872" s="3" t="b">
         <v>0</v>
@@ -28904,7 +28904,7 @@
         <v>1</v>
       </c>
       <c r="C878" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D878" s="3" t="b">
         <v>0</v>
@@ -29032,7 +29032,7 @@
         <v>1</v>
       </c>
       <c r="C882" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D882" s="3" t="b">
         <v>1</v>
@@ -29064,7 +29064,7 @@
         <v>0</v>
       </c>
       <c r="C883" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D883" s="3" t="b">
         <v>1</v>
@@ -29096,7 +29096,7 @@
         <v>1</v>
       </c>
       <c r="C884" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D884" s="3" t="b">
         <v>1</v>
@@ -29224,7 +29224,7 @@
         <v>0</v>
       </c>
       <c r="C888" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D888" s="3" t="b">
         <v>0</v>
@@ -29288,7 +29288,7 @@
         <v>0</v>
       </c>
       <c r="C890" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D890" s="3" t="b">
         <v>0</v>
@@ -29352,7 +29352,7 @@
         <v>1</v>
       </c>
       <c r="C892" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D892" s="3" t="b">
         <v>0</v>
@@ -29448,7 +29448,7 @@
         <v>1</v>
       </c>
       <c r="C895" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D895" s="3" t="b">
         <v>0</v>
@@ -29480,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="C896" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D896" s="3" t="b">
         <v>0</v>
@@ -29512,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="C897" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D897" s="3" t="b">
         <v>0</v>
@@ -29544,7 +29544,7 @@
         <v>1</v>
       </c>
       <c r="C898" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D898" s="3" t="b">
         <v>0</v>
@@ -29640,7 +29640,7 @@
         <v>1</v>
       </c>
       <c r="C901" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D901" s="3" t="b">
         <v>0</v>
@@ -29704,7 +29704,7 @@
         <v>1</v>
       </c>
       <c r="C903" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D903" s="3" t="b">
         <v>1</v>
@@ -29736,7 +29736,7 @@
         <v>1</v>
       </c>
       <c r="C904" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D904" s="3" t="b">
         <v>1</v>
@@ -29800,7 +29800,7 @@
         <v>1</v>
       </c>
       <c r="C906" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D906" s="3" t="b">
         <v>1</v>
@@ -29832,7 +29832,7 @@
         <v>1</v>
       </c>
       <c r="C907" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D907" s="3" t="b">
         <v>1</v>
@@ -29992,7 +29992,7 @@
         <v>1</v>
       </c>
       <c r="C912" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D912" s="3" t="b">
         <v>1</v>
@@ -30184,7 +30184,7 @@
         <v>1</v>
       </c>
       <c r="C918" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D918" s="3" t="b">
         <v>1</v>
@@ -30344,7 +30344,7 @@
         <v>1</v>
       </c>
       <c r="C923" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D923" s="3" t="b">
         <v>1</v>
@@ -30376,7 +30376,7 @@
         <v>1</v>
       </c>
       <c r="C924" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D924" s="3" t="b">
         <v>1</v>
@@ -30408,7 +30408,7 @@
         <v>1</v>
       </c>
       <c r="C925" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D925" s="3" t="b">
         <v>1</v>
@@ -30568,7 +30568,7 @@
         <v>1</v>
       </c>
       <c r="C930" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D930" s="3" t="b">
         <v>1</v>
@@ -32680,7 +32680,7 @@
         <v>0</v>
       </c>
       <c r="C996" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D996" s="3" t="b">
         <v>1</v>
